--- a/02_experimental_validation/plasmids/pET-11a/pET11a_Synthesis.xlsx
+++ b/02_experimental_validation/plasmids/pET-11a/pET11a_Synthesis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jackylin/Documents/GitHub/LiSPER/02_experimental_validation/plasmids/pET-11a/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518E5935-B19F-B349-BE88-26228F0263C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002B8FA2-5301-514F-8B05-F6130E1E4370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="2740" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9640" yWindow="3740" windowWidth="36300" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthesis" sheetId="1" r:id="rId1"/>
@@ -398,7 +398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="112.5" customHeight="1">
+    <row r="2" spans="1:4" ht="121" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -412,7 +412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="112.5" customHeight="1">
+    <row r="3" spans="1:4" ht="130" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -426,7 +426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="112.5" customHeight="1">
+    <row r="4" spans="1:4" ht="133" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -440,7 +440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="112.5" customHeight="1">
+    <row r="5" spans="1:4" ht="141" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -454,7 +454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="112.5" customHeight="1">
+    <row r="6" spans="1:4" ht="133" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
